--- a/english-study-template.xlsx
+++ b/english-study-template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B129"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -413,31 +413,1031 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Hello, world!</v>
+        <v>a quarter of</v>
       </c>
       <c r="B2" t="str">
-        <v>你好，世界！</v>
+        <v>四分之一...</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>I love learning English.</v>
+        <v>a half of</v>
       </c>
       <c r="B3" t="str">
-        <v>我喜欢学英语。</v>
+        <v>一半...</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Practice makes perfect.</v>
+        <v>collect</v>
       </c>
       <c r="B4" t="str">
-        <v>熟能生巧。</v>
+        <v>收集</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>collector</v>
+      </c>
+      <c r="B5" t="str">
+        <v>收集者</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>collection</v>
+      </c>
+      <c r="B6" t="str">
+        <v>收集品、收集物</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>collect sunshine</v>
+      </c>
+      <c r="B7" t="str">
+        <v>收集阳光</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>have a collection of...</v>
+      </c>
+      <c r="B8" t="str">
+        <v>有...的收藏</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>send</v>
+      </c>
+      <c r="B9" t="str">
+        <v>发送、送出、派遣</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>send up</v>
+      </c>
+      <c r="B10" t="str">
+        <v>发射</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>send into</v>
+      </c>
+      <c r="B11" t="str">
+        <v>送入</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>send out</v>
+      </c>
+      <c r="B12" t="str">
+        <v>发出、放出</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>send sb sth = send sth to sb</v>
+      </c>
+      <c r="B13" t="str">
+        <v>给某人送某物</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>send sb to do</v>
+      </c>
+      <c r="B14" t="str">
+        <v>派某人去做某事</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>send sb. to sp.</v>
+      </c>
+      <c r="B15" t="str">
+        <v>派某人去某地</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>rise</v>
+      </c>
+      <c r="B16" t="str">
+        <v>上升</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>rise up</v>
+      </c>
+      <c r="B17" t="str">
+        <v>升起</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>rise up to the leaf</v>
+      </c>
+      <c r="B18" t="str">
+        <v>升到树叶</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>mix</v>
+      </c>
+      <c r="B19" t="str">
+        <v>混合</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>mixture</v>
+      </c>
+      <c r="B20" t="str">
+        <v>混合物</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>mix A and B = mix A with B</v>
+      </c>
+      <c r="B21" t="str">
+        <v>把A和B混合在一起</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>a mixture of sth</v>
+      </c>
+      <c r="B22" t="str">
+        <v>…的混合物</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>produce</v>
+      </c>
+      <c r="B23" t="str">
+        <v>生产、产生、制造、引起</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>production</v>
+      </c>
+      <c r="B24" t="str">
+        <v>生产、产量</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>product</v>
+      </c>
+      <c r="B25" t="str">
+        <v>产品、生成物</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>breathe</v>
+      </c>
+      <c r="B26" t="str">
+        <v>呼吸</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>breath</v>
+      </c>
+      <c r="B27" t="str">
+        <v>呼吸，气息</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>breathe in</v>
+      </c>
+      <c r="B28" t="str">
+        <v>吸气</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>breathe out</v>
+      </c>
+      <c r="B29" t="str">
+        <v>呼气</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>get dark</v>
+      </c>
+      <c r="B30" t="str">
+        <v>变黑</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>in the dark</v>
+      </c>
+      <c r="B31" t="str">
+        <v>在黑暗里</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>take a rest = take a break</v>
+      </c>
+      <c r="B32" t="str">
+        <v>休息</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>the rest of …</v>
+      </c>
+      <c r="B33" t="str">
+        <v>剩余的...</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>nature</v>
+      </c>
+      <c r="B34" t="str">
+        <v>自然</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>natural</v>
+      </c>
+      <c r="B35" t="str">
+        <v>自然的</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>explore the amazing world of plants</v>
+      </c>
+      <c r="B36" t="str">
+        <v>探索神秘的植物世界</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>start to do</v>
+      </c>
+      <c r="B37" t="str">
+        <v>开始去做某事</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>start doing</v>
+      </c>
+      <c r="B38" t="str">
+        <v>开始做了某事</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>start ... with ...</v>
+      </c>
+      <c r="B39" t="str">
+        <v>以...开始</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>work in</v>
+      </c>
+      <c r="B40" t="str">
+        <v>在…工作</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>in each workshop</v>
+      </c>
+      <c r="B41" t="str">
+        <v>在每一个车间</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>through the stem</v>
+      </c>
+      <c r="B42" t="str">
+        <v>通过茎</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>be useful to sb./ for sth.</v>
+      </c>
+      <c r="B43" t="str">
+        <v>对…有用</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>the growth of the plant</v>
+      </c>
+      <c r="B44" t="str">
+        <v>植物的生长</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>mean to do</v>
+      </c>
+      <c r="B45" t="str">
+        <v>打算做某事</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>mean a lot</v>
+      </c>
+      <c r="B46" t="str">
+        <v>意味着很多</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>mean doing</v>
+      </c>
+      <c r="B47" t="str">
+        <v>意味着…</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>mean sth to sb</v>
+      </c>
+      <c r="B48" t="str">
+        <v>对某人来说意味着…</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>millions of plants</v>
+      </c>
+      <c r="B49" t="str">
+        <v>几百万棵植物</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>more than</v>
+      </c>
+      <c r="B50" t="str">
+        <v>不仅仅</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>be sure that</v>
+      </c>
+      <c r="B51" t="str">
+        <v>确信，确定…</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>at the top of</v>
+      </c>
+      <c r="B52" t="str">
+        <v>在…的顶端</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>come into</v>
+      </c>
+      <c r="B53" t="str">
+        <v>进入到…</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>do something for sb</v>
+      </c>
+      <c r="B54" t="str">
+        <v>对某人做某事</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>grow</v>
+      </c>
+      <c r="B55" t="str">
+        <v>成长</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>growth</v>
+      </c>
+      <c r="B56" t="str">
+        <v>成长</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>grow up</v>
+      </c>
+      <c r="B57" t="str">
+        <v>长大</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>a big part of</v>
+      </c>
+      <c r="B58" t="str">
+        <v>大部分</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>culture</v>
+      </c>
+      <c r="B59" t="str">
+        <v>文化</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>cultural</v>
+      </c>
+      <c r="B60" t="str">
+        <v>文化的</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>top three</v>
+      </c>
+      <c r="B61" t="str">
+        <v>前三</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>the world's top three food plants</v>
+      </c>
+      <c r="B62" t="str">
+        <v>世界前三的食物植物</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>people around the world</v>
+      </c>
+      <c r="B63" t="str">
+        <v>全世界的人</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>in different ways</v>
+      </c>
+      <c r="B64" t="str">
+        <v>以不同的方法</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>in East Asia</v>
+      </c>
+      <c r="B65" t="str">
+        <v>在东亚</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>about 900 years ago</v>
+      </c>
+      <c r="B66" t="str">
+        <v>大约900年以前</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>over 600 corn dishes</v>
+      </c>
+      <c r="B67" t="str">
+        <v>大约600种玉米餐食</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>use …as</v>
+      </c>
+      <c r="B68" t="str">
+        <v>使用…作为…</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>use sth to do</v>
+      </c>
+      <c r="B69" t="str">
+        <v>使用…做</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>use it to make toys</v>
+      </c>
+      <c r="B70" t="str">
+        <v>使用它做玩具</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>use … for</v>
+      </c>
+      <c r="B71" t="str">
+        <v>为了…使用…</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>pay attention to</v>
+      </c>
+      <c r="B72" t="str">
+        <v>注意、留意</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>a traditional Mexican food</v>
+      </c>
+      <c r="B73" t="str">
+        <v>一个传统的墨西哥食物</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>make ... from</v>
+      </c>
+      <c r="B74" t="str">
+        <v>用…制作（看不出原材料）</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>make ... with</v>
+      </c>
+      <c r="B75" t="str">
+        <v>用…制作</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>be made from</v>
+      </c>
+      <c r="B76" t="str">
+        <v>由…制作（看不出原材料）</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>be made of</v>
+      </c>
+      <c r="B77" t="str">
+        <v>由…制作（看得出原材料）</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>be good for your health</v>
+      </c>
+      <c r="B78" t="str">
+        <v>对你的健康有好处</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>the way of doing</v>
+      </c>
+      <c r="B79" t="str">
+        <v>做某事的方法</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>the way to do</v>
+      </c>
+      <c r="B80" t="str">
+        <v>做某事的方法</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>try to do</v>
+      </c>
+      <c r="B81" t="str">
+        <v>努力做某事</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>try one's best to do</v>
+      </c>
+      <c r="B82" t="str">
+        <v>尽某人最大努力做某事</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>try doing sth</v>
+      </c>
+      <c r="B83" t="str">
+        <v>试着做某事</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>give permission</v>
+      </c>
+      <c r="B84" t="str">
+        <v>允许、准许</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>health</v>
+      </c>
+      <c r="B85" t="str">
+        <v>健康</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>healthy</v>
+      </c>
+      <c r="B86" t="str">
+        <v>健康的</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>health problem</v>
+      </c>
+      <c r="B87" t="str">
+        <v>健康问题</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>keep healthy</v>
+      </c>
+      <c r="B88" t="str">
+        <v>保持健康</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>be popular with</v>
+      </c>
+      <c r="B89" t="str">
+        <v>在…中流行, 受...的欢迎</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>the key to the door</v>
+      </c>
+      <c r="B90" t="str">
+        <v>门的钥匙</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>the key part of</v>
+      </c>
+      <c r="B91" t="str">
+        <v>主要部分</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>a piece of news</v>
+      </c>
+      <c r="B92" t="str">
+        <v>一条信息</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>the secret of sth.</v>
+      </c>
+      <c r="B93" t="str">
+        <v>…的秘密</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>keep a secret</v>
+      </c>
+      <c r="B94" t="str">
+        <v>保持秘密</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>chat</v>
+      </c>
+      <c r="B95" t="str">
+        <v>聊天</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>chat on the phone</v>
+      </c>
+      <c r="B96" t="str">
+        <v>电话聊天</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>chat to / with sb</v>
+      </c>
+      <c r="B97" t="str">
+        <v>和某人聊天</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>chat about</v>
+      </c>
+      <c r="B98" t="str">
+        <v>聊某事</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>relax oneself</v>
+      </c>
+      <c r="B99" t="str">
+        <v>放松自己</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>connect</v>
+      </c>
+      <c r="B100" t="str">
+        <v>链接、联系</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>connection</v>
+      </c>
+      <c r="B101" t="str">
+        <v>链接、联系</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>connect A to B</v>
+      </c>
+      <c r="B102" t="str">
+        <v>把A 连到B上</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>connect A with B</v>
+      </c>
+      <c r="B103" t="str">
+        <v>把A和B连起来</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>connection between A and B</v>
+      </c>
+      <c r="B104" t="str">
+        <v>A和B之间的联系</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>not only… but also…</v>
+      </c>
+      <c r="B105" t="str">
+        <v>不但…而且…</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>as…as</v>
+      </c>
+      <c r="B106" t="str">
+        <v>和…一样（中间加原级）</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>as many teahouses as leaves in the cup of tea</v>
+      </c>
+      <c r="B107" t="str">
+        <v>茶馆和杯子里的茶叶一样多</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>used to do</v>
+      </c>
+      <c r="B108" t="str">
+        <v>过去常常做某事</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>get / be used to doing</v>
+      </c>
+      <c r="B109" t="str">
+        <v>习惯做某事</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>be used to do</v>
+      </c>
+      <c r="B110" t="str">
+        <v>被用来去做</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>share sth with sb</v>
+      </c>
+      <c r="B111" t="str">
+        <v>和某人分享…</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>share their news</v>
+      </c>
+      <c r="B112" t="str">
+        <v>分享他们的消息</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>study abroad</v>
+      </c>
+      <c r="B113" t="str">
+        <v>出国学习</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>prefer A to B</v>
+      </c>
+      <c r="B114" t="str">
+        <v>比起B更喜欢A</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>prefer doing A to doing B</v>
+      </c>
+      <c r="B115" t="str">
+        <v>比起做B更喜欢做A</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>prefer to do</v>
+      </c>
+      <c r="B116" t="str">
+        <v>更喜欢做某事</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>prefer to do A rather than do B</v>
+      </c>
+      <c r="B117" t="str">
+        <v>宁愿做…也不做</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>a cup of warm tea</v>
+      </c>
+      <c r="B118" t="str">
+        <v>一杯热茶</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>feel like</v>
+      </c>
+      <c r="B119" t="str">
+        <v>感觉像</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>It's no secret that…</v>
+      </c>
+      <c r="B120" t="str">
+        <v>众所周知</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>make tea for them</v>
+      </c>
+      <c r="B121" t="str">
+        <v>为他们泡茶</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>choose</v>
+      </c>
+      <c r="B122" t="str">
+        <v>选择</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>choice</v>
+      </c>
+      <c r="B123" t="str">
+        <v>选择</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>compare</v>
+      </c>
+      <c r="B124" t="str">
+        <v>比较</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>comparison</v>
+      </c>
+      <c r="B125" t="str">
+        <v>比较</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>compare A with B</v>
+      </c>
+      <c r="B126" t="str">
+        <v>把A和B相比较</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>compare A to B</v>
+      </c>
+      <c r="B127" t="str">
+        <v>把A比作B</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>be similar to sth</v>
+      </c>
+      <c r="B128" t="str">
+        <v>和…相似</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>search for sth</v>
+      </c>
+      <c r="B129" t="str">
+        <v>查找、搜寻</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
   </ignoredErrors>
 </worksheet>
 </file>